--- a/reports/meta_intel_2026-W26.xlsx
+++ b/reports/meta_intel_2026-W26.xlsx
@@ -457,7 +457,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Generated: 2026-06-22 11:07 UTC</t>
+          <t>Generated: 2026-06-22 17:48 UTC</t>
         </is>
       </c>
     </row>
@@ -469,7 +469,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>98</v>
+        <v>87</v>
       </c>
     </row>
     <row r="5">
@@ -479,7 +479,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>98</v>
+        <v>87</v>
       </c>
     </row>
     <row r="6">
@@ -551,7 +551,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>23</v>
+        <v>18</v>
       </c>
     </row>
     <row r="14">
@@ -561,7 +561,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
     </row>
     <row r="15">
@@ -665,12 +665,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J99"/>
+  <dimension ref="A1:J88"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
     <col width="19" customWidth="1" min="2" max="2"/>
-    <col width="60" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
     <col width="80" customWidth="1" min="4" max="4"/>
     <col width="60" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
@@ -945,31 +945,31 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2589188208165366</t>
+          <t>27880751554865955</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Cortney Belnap, Independent Norwex Consultant with Remento</t>
+          <t>Remento</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>With Remento, preserving precious stories is as easy as having a conversation. They will simply speak, and Remento will do the rest. Turning their spoken words into professionally written stories. Each story is paired with a QR code that when scanned, links back to original recordings. This way, you can watch or listen to them anytime as they tell their story. 👆 Pick storytelling prompts/photos 📱 Record spoken answers</t>
+          <t>Want to capture your loved one's life story without the hassle of writing and typing? Introducing Remento! Tim Ferriss chose it for his mom, calling it an "A+ investment!" • 80% of life stories are never recorded - don't let that be yours!</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>📖 Remento turns recordings into a book of written stories</t>
+          <t>Give Remento as a gift &amp; turn memories into a stunning interactive book.</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="I7" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
@@ -985,7 +985,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>1644683516797904</t>
+          <t>1001223935838093</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1005,11 +1005,11 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="I8" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
@@ -1025,7 +1025,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>27880751554865955</t>
+          <t>2222090038553123</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1035,21 +1035,21 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Want to capture your loved one's life story without the hassle of writing and typing? Introducing Remento! Tim Ferriss chose it for his mom, calling it an "A+ investment!" • 80% of life stories are never recorded - don't let that be yours!</t>
+          <t>As seen on Shark Tank: the ONLY book dad writes without writing a word, AND it has his voice inside. Why dad's love it: 📱 No downloads, logins, or passwords</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Give Remento as a gift &amp; turn memories into a stunning interactive book.</t>
+          <t>✍️ Speech-to-Story writes for them (without changing their voice)</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="I9" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
@@ -1065,7 +1065,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>1001223935838093</t>
+          <t>1683371159589008</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1075,21 +1075,26 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>With Remento, preserving precious stories is as easy as having a conversation. They will simply speak, and Remento will do the rest. Turning their spoken words into professionally written stories. Each story is paired with a QR code that when scanned, links back to original recordings. This way, you can watch or listen to them anytime as they tell their story. 👆 Pick storytelling prompts/photos 📱 Record spoken answers</t>
+          <t>I decided I wasn't going to miss the chance to ask so many more questions... Make history for your family. Give a loved one Remento, not a writing assignment, and their timeless stories will be captured forever for the whole family in an interactive hardcover book. Sorry, we're having trouble playing this video.</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>📖 Remento turns recordings into a book of written stories</t>
+          <t>Sorry, we're having trouble playing this video.</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Learn more</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="I10" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
@@ -1105,7 +1110,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2222090038553123</t>
+          <t>1786057292771309</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1115,7 +1120,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>As seen on Shark Tank: the ONLY book dad writes without writing a word, AND it has his voice inside. Why dad's love it: 📱 No downloads, logins, or passwords</t>
+          <t>The most meaningful Father’s Day gift: his voice, forever at your fingertips. Why families love it: 📱 No downloads, logins, or passwords</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -1125,11 +1130,11 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="I11" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
@@ -1145,7 +1150,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>1683371159589008</t>
+          <t>1913150252681632</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1155,26 +1160,21 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>I decided I wasn't going to miss the chance to ask so many more questions... Make history for your family. Give a loved one Remento, not a writing assignment, and their timeless stories will be captured forever for the whole family in an interactive hardcover book. Sorry, we're having trouble playing this video.</t>
+          <t>The most meaningful Father’s Day gift: his voice, forever at your fingertips. Why families love it: 📱 No downloads, logins, or passwords</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Sorry, we're having trouble playing this video.</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>Learn more</t>
+          <t>✍️ Speech-to-Story writes for them (without changing their voice)</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="I12" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
@@ -1190,7 +1190,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>1751531616005068</t>
+          <t>1278795710734763</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1200,12 +1200,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>As seen on Shark Tank: the ONLY book dad writes without writing a word, AND it has his voice inside. Why dad's love it: 📱 No downloads, logins, or passwords</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>✍️ Speech-to-Story writes for them (without changing their voice)</t>
+          <t>His story is YOUR story too. His favorite gift delivers in seconds ⌛️🎁 Gift Dad Remento, not a writing assignment, and his timeless stories will be captured forever for the whole family in an interactive hardcover book.</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -1230,7 +1225,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>1786057292771309</t>
+          <t>1555465969317444</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1240,21 +1235,21 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>The most meaningful Father’s Day gift: his voice, forever at your fingertips. Why families love it: 📱 No downloads, logins, or passwords</t>
+          <t>With Remento, preserving precious stories is as easy as having a conversation. They will simply speak, and Remento will do the rest. Turning their spoken words into professionally written stories. Each story is paired with a QR code that when scanned, links back to original recordings. This way, you can watch or listen to them anytime as they tell their story. 👆 Pick storytelling prompts/photos 📱 Record spoken answers</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>✍️ Speech-to-Story writes for them (without changing their voice)</t>
+          <t>📖 Remento turns recordings into a book of written stories</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="I14" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
@@ -1270,31 +1265,31 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2915078732162013</t>
+          <t>1036735562201821</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Cortney Belnap, Independent Norwex Consultant with Remento</t>
+          <t>Remento</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>As seen on Shark Tank: the ONLY book dad writes without writing a word, AND it has his voice inside. Why dad's love it: 📱 No downloads, logins, or passwords</t>
+          <t>With Remento, preserving precious stories is as easy as having a conversation. They will simply speak, and Remento will do the rest. Turning their spoken words into professionally written stories. Each story is paired with a QR code that when scanned, links back to original recordings. This way, you can watch or listen to them anytime as they tell their story. 👆 Pick storytelling prompts/photos 📱 Record spoken answers</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>✍️ Speech-to-Story writes for them (without changing their voice)</t>
+          <t>📖 Remento turns recordings into a book of written stories</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="I15" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
@@ -1310,7 +1305,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>1913150252681632</t>
+          <t>1024756963571760</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1320,21 +1315,21 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>The most meaningful Father’s Day gift: his voice, forever at your fingertips. Why families love it: 📱 No downloads, logins, or passwords</t>
+          <t>With Remento, preserving precious stories is as easy as having a conversation. They will simply speak, and Remento will do the rest. Turning their spoken words into professionally written stories. Each story is paired with a QR code that when scanned, links back to original recordings. This way, you can watch or listen to them anytime as they tell their story. 👆 Pick storytelling prompts/photos 📱 Record spoken answers</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>✍️ Speech-to-Story writes for them (without changing their voice)</t>
+          <t>📖 Remento turns recordings into a book of written stories</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="I16" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>
@@ -1350,7 +1345,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>1278795710734763</t>
+          <t>2248159552601062</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1360,16 +1355,21 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>His story is YOUR story too. His favorite gift delivers in seconds ⌛️🎁 Gift Dad Remento, not a writing assignment, and his timeless stories will be captured forever for the whole family in an interactive hardcover book.</t>
+          <t>With Remento, preserving precious stories is as easy as having a conversation. They will simply speak, and Remento will do the rest. Turning their spoken words into professionally written stories. Each story is paired with a QR code that when scanned, links back to original recordings. This way, you can watch or listen to them anytime as they tell their story. 👆 Pick storytelling prompts/photos 📱 Record spoken answers</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>📖 Remento turns recordings into a book of written stories</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="I17" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
@@ -1385,7 +1385,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>1555465969317444</t>
+          <t>2129791074419999</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1395,21 +1395,26 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>With Remento, preserving precious stories is as easy as having a conversation. They will simply speak, and Remento will do the rest. Turning their spoken words into professionally written stories. Each story is paired with a QR code that when scanned, links back to original recordings. This way, you can watch or listen to them anytime as they tell their story. 👆 Pick storytelling prompts/photos 📱 Record spoken answers</t>
+          <t>The Sharks were truly moved by this pitch #sharktank Sorry, we're having trouble playing this video.</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>📖 Remento turns recordings into a book of written stories</t>
+          <t>Sorry, we're having trouble playing this video.</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Learn more</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="I18" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>
@@ -1425,7 +1430,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>1036735562201821</t>
+          <t>1932125440830258</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1445,11 +1450,11 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="I19" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="J19" t="inlineStr">
         <is>
@@ -1460,36 +1465,36 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Remento</t>
+          <t>Enna</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>1024756963571760</t>
+          <t>1868277354563662</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Remento</t>
+          <t>enna.care</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>With Remento, preserving precious stories is as easy as having a conversation. They will simply speak, and Remento will do the rest. Turning their spoken words into professionally written stories. Each story is paired with a QR code that when scanned, links back to original recordings. This way, you can watch or listen to them anytime as they tell their story. 👆 Pick storytelling prompts/photos 📱 Record spoken answers</t>
+          <t>Mit enna bleiben Generationen verbunden: ✅ Erinnerungen schicken ✅ Große Auswahl an Unterhaltung</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>📖 Remento turns recordings into a book of written stories</t>
+          <t>Kein Kauf, keine Einrichtung.</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="I20" t="n">
-        <v>4</v>
+        <v>220</v>
       </c>
       <c r="J20" t="inlineStr">
         <is>
@@ -1500,36 +1505,36 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Remento</t>
+          <t>Enna</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2248159552601062</t>
+          <t>1362684515702149</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Remento</t>
+          <t>enna.care</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>With Remento, preserving precious stories is as easy as having a conversation. They will simply speak, and Remento will do the rest. Turning their spoken words into professionally written stories. Each story is paired with a QR code that when scanned, links back to original recordings. This way, you can watch or listen to them anytime as they tell their story. 👆 Pick storytelling prompts/photos 📱 Record spoken answers</t>
+          <t>Mit enna bleiben Generationen verbunden: ✅ Erinnerungen schicken ✅ Große Auswahl an Unterhaltung</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>📖 Remento turns recordings into a book of written stories</t>
+          <t>Kein Kauf, keine Einrichtung.</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="I21" t="n">
-        <v>6</v>
+        <v>55</v>
       </c>
       <c r="J21" t="inlineStr">
         <is>
@@ -1540,41 +1545,36 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Remento</t>
+          <t>Enna</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2129791074419999</t>
+          <t>1938930663325095</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Remento</t>
+          <t>enna.care</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>The Sharks were truly moved by this pitch #sharktank Sorry, we're having trouble playing this video.</t>
+          <t>Mit enna bleiben Generationen verbunden: ✅ Erinnerungen schicken ✅ Große Auswahl an Unterhaltung</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Sorry, we're having trouble playing this video.</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>Learn more</t>
+          <t>Kein Kauf, keine Einrichtung.</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="I22" t="n">
-        <v>6</v>
+        <v>220</v>
       </c>
       <c r="J22" t="inlineStr">
         <is>
@@ -1585,36 +1585,36 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Remento</t>
+          <t>Enna</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2245313849547808</t>
+          <t>1588345672369492</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>timabous with Remento</t>
+          <t>enna.care</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Most families have boxes of old photos sitting in closets, attics, or drawers. That’s why we love this partnership: 📸 Legacybox helps digitize and preserve old family photos.</t>
+          <t>Mit enna bleiben Generationen verbunden: ✅ Erinnerungen schicken ✅ Große Auswahl an Unterhaltung</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>🎙️ Remento captures the stories behind those photos - in your loved one’s own voice.</t>
+          <t>Kein Kauf, keine Einrichtung.</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="I23" t="n">
-        <v>11</v>
+        <v>131</v>
       </c>
       <c r="J23" t="inlineStr">
         <is>
@@ -1625,36 +1625,36 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Remento</t>
+          <t>Enna</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>1932125440830258</t>
+          <t>1852060685669387</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Remento</t>
+          <t>enna.care</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>With Remento, preserving precious stories is as easy as having a conversation. They will simply speak, and Remento will do the rest. Turning their spoken words into professionally written stories. Each story is paired with a QR code that when scanned, links back to original recordings. This way, you can watch or listen to them anytime as they tell their story. 👆 Pick storytelling prompts/photos 📱 Record spoken answers</t>
+          <t>Mit enna bleiben Generationen verbunden: ✅ Erinnerungen schicken ✅ Große Auswahl an Unterhaltung</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>📖 Remento turns recordings into a book of written stories</t>
+          <t>Kein Kauf, keine Einrichtung.</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="I24" t="n">
-        <v>4</v>
+        <v>227</v>
       </c>
       <c r="J24" t="inlineStr">
         <is>
@@ -1670,7 +1670,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>1868277354563662</t>
+          <t>841302105060560</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1690,11 +1690,11 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="I25" t="n">
-        <v>220</v>
+        <v>227</v>
       </c>
       <c r="J25" t="inlineStr">
         <is>
@@ -1710,7 +1710,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>1362684515702149</t>
+          <t>1296748252140081</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1730,11 +1730,11 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="I26" t="n">
-        <v>55</v>
+        <v>227</v>
       </c>
       <c r="J26" t="inlineStr">
         <is>
@@ -1750,7 +1750,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>1938930663325095</t>
+          <t>3976129939359406</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1770,11 +1770,11 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="I27" t="n">
-        <v>220</v>
+        <v>227</v>
       </c>
       <c r="J27" t="inlineStr">
         <is>
@@ -1790,7 +1790,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>1588345672369492</t>
+          <t>1943193019573119</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1810,11 +1810,11 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="I28" t="n">
-        <v>131</v>
+        <v>227</v>
       </c>
       <c r="J28" t="inlineStr">
         <is>
@@ -1830,7 +1830,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>1852060685669387</t>
+          <t>4072587919646468</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1850,11 +1850,11 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2026-04-12</t>
         </is>
       </c>
       <c r="I29" t="n">
-        <v>227</v>
+        <v>71</v>
       </c>
       <c r="J29" t="inlineStr">
         <is>
@@ -1870,7 +1870,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>841302105060560</t>
+          <t>2260190851070799</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1890,11 +1890,11 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="I30" t="n">
-        <v>227</v>
+        <v>220</v>
       </c>
       <c r="J30" t="inlineStr">
         <is>
@@ -1910,7 +1910,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>1296748252140081</t>
+          <t>796404973298946</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1950,7 +1950,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>3976129939359406</t>
+          <t>3727759467519562</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1970,11 +1970,11 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="I32" t="n">
-        <v>227</v>
+        <v>220</v>
       </c>
       <c r="J32" t="inlineStr">
         <is>
@@ -1990,7 +1990,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>1943193019573119</t>
+          <t>1549478262721918</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2030,7 +2030,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>4072587919646468</t>
+          <t>1171548231746967</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2050,11 +2050,11 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>2026-04-12</t>
+          <t>2025-11-15</t>
         </is>
       </c>
       <c r="I34" t="n">
-        <v>71</v>
+        <v>219</v>
       </c>
       <c r="J34" t="inlineStr">
         <is>
@@ -2070,7 +2070,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2260190851070799</t>
+          <t>871339118687590</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2080,7 +2080,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Mit enna bleiben Generationen verbunden: ✅ Erinnerungen schicken ✅ Große Auswahl an Unterhaltung</t>
+          <t>Mach auch deine Oma glücklich &amp; bring die ganze Familie näher zusammen! 🥰 ✅ Erinnerungen &amp; Nachrichten schicken ✅ Große Auswahl an Unterhaltung</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -2090,11 +2090,11 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2026-01-22</t>
         </is>
       </c>
       <c r="I35" t="n">
-        <v>220</v>
+        <v>151</v>
       </c>
       <c r="J35" t="inlineStr">
         <is>
@@ -2110,7 +2110,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>796404973298946</t>
+          <t>2761672647588250</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2130,11 +2130,11 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="I36" t="n">
-        <v>227</v>
+        <v>131</v>
       </c>
       <c r="J36" t="inlineStr">
         <is>
@@ -2150,7 +2150,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>3727759467519562</t>
+          <t>1628987998235230</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2170,11 +2170,11 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="I37" t="n">
-        <v>220</v>
+        <v>117</v>
       </c>
       <c r="J37" t="inlineStr">
         <is>
@@ -2190,7 +2190,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>1549478262721918</t>
+          <t>804595359053733</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2210,11 +2210,11 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="I38" t="n">
-        <v>227</v>
+        <v>220</v>
       </c>
       <c r="J38" t="inlineStr">
         <is>
@@ -2230,7 +2230,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>1171548231746967</t>
+          <t>25607802815471461</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2250,11 +2250,11 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>2025-11-15</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="I39" t="n">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="J39" t="inlineStr">
         <is>
@@ -2270,7 +2270,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>871339118687590</t>
+          <t>1373162224393589</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2280,7 +2280,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Mach auch deine Oma glücklich &amp; bring die ganze Familie näher zusammen! 🥰 ✅ Erinnerungen &amp; Nachrichten schicken ✅ Große Auswahl an Unterhaltung</t>
+          <t>Mit enna bleiben Generationen verbunden: ✅ Erinnerungen schicken ✅ Große Auswahl an Unterhaltung</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -2290,11 +2290,11 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>2026-01-22</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="I40" t="n">
-        <v>151</v>
+        <v>227</v>
       </c>
       <c r="J40" t="inlineStr">
         <is>
@@ -2310,7 +2310,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2761672647588250</t>
+          <t>1896813954581984</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2330,11 +2330,11 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="I41" t="n">
-        <v>131</v>
+        <v>227</v>
       </c>
       <c r="J41" t="inlineStr">
         <is>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>1628987998235230</t>
+          <t>779152008120335</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2370,11 +2370,11 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="I42" t="n">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="J42" t="inlineStr">
         <is>
@@ -2390,7 +2390,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>804595359053733</t>
+          <t>809944418627988</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -2410,11 +2410,11 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="I43" t="n">
-        <v>220</v>
+        <v>227</v>
       </c>
       <c r="J43" t="inlineStr">
         <is>
@@ -2430,7 +2430,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>25607802815471461</t>
+          <t>4246986475583692</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -2450,11 +2450,11 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="I44" t="n">
-        <v>220</v>
+        <v>227</v>
       </c>
       <c r="J44" t="inlineStr">
         <is>
@@ -2470,7 +2470,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>1373162224393589</t>
+          <t>2337622166699478</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -2490,11 +2490,11 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="I45" t="n">
-        <v>227</v>
+        <v>220</v>
       </c>
       <c r="J45" t="inlineStr">
         <is>
@@ -2510,7 +2510,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>1896813954581984</t>
+          <t>1226905979591545</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -2530,11 +2530,11 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="I46" t="n">
-        <v>227</v>
+        <v>131</v>
       </c>
       <c r="J46" t="inlineStr">
         <is>
@@ -2550,7 +2550,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>779152008120335</t>
+          <t>4227670180779906</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -2570,11 +2570,11 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-14</t>
         </is>
       </c>
       <c r="I47" t="n">
-        <v>116</v>
+        <v>128</v>
       </c>
       <c r="J47" t="inlineStr">
         <is>
@@ -2590,7 +2590,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>809944418627988</t>
+          <t>1545507783219388</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -2600,21 +2600,21 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Mit enna bleiben Generationen verbunden: ✅ Erinnerungen schicken ✅ Große Auswahl an Unterhaltung</t>
+          <t>Next Level Kommunikation mit Oma 🫶 Dank enna auch ohne Smartphone: ✅ Erinnerungen schicken</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Kein Kauf, keine Einrichtung.</t>
+          <t>✅ Große Auswahl an Unterhaltung</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="I48" t="n">
-        <v>227</v>
+        <v>117</v>
       </c>
       <c r="J48" t="inlineStr">
         <is>
@@ -2625,36 +2625,36 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Enna</t>
+          <t>Storykeeper</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>4246986475583692</t>
+          <t>1366264645392236</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>enna.care</t>
+          <t>StoryKeeper</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Mit enna bleiben Generationen verbunden: ✅ Erinnerungen schicken ✅ Große Auswahl an Unterhaltung</t>
+          <t>This Mother's Day, give her a gift that will last forever! Turn her life story into a personalized book filled with memories and love. What would she say if you asked about her most cherished moments?</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Kein Kauf, keine Einrichtung.</t>
+          <t>Sorry, we're having trouble playing this video.</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="I49" t="n">
-        <v>227</v>
+        <v>6</v>
       </c>
       <c r="J49" t="inlineStr">
         <is>
@@ -2665,36 +2665,41 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Enna</t>
+          <t>Storykeeper</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2337622166699478</t>
+          <t>1497596251413526</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>enna.care</t>
+          <t>StoryKeeper</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Mit enna bleiben Generationen verbunden: ✅ Erinnerungen schicken ✅ Große Auswahl an Unterhaltung</t>
+          <t>Give him a lifetime of memories instead of another throwaway present. Start his StoryKeeper book today. Skip the generic Father’s Day gifts Give him a lifetime of memories.</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Kein Kauf, keine Einrichtung.</t>
+          <t>Give him a lifetime of memories.</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Shop now</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="I50" t="n">
-        <v>220</v>
+        <v>3</v>
       </c>
       <c r="J50" t="inlineStr">
         <is>
@@ -2705,36 +2710,36 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Enna</t>
+          <t>Storykeeper</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>1226905979591545</t>
+          <t>26907492185598691</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>enna.care</t>
+          <t>StoryKeeper</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Mit enna bleiben Generationen verbunden: ✅ Erinnerungen schicken ✅ Große Auswahl an Unterhaltung</t>
+          <t>Give more than a gift—give your family a keepsake that grows more meaningful with time. WWW.STORYKEEPER.UK The Gift They’ll Never Forget.</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Kein Kauf, keine Einrichtung.</t>
+          <t>Give a gift that becomes a family heirloom—one story at a time.</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="I51" t="n">
-        <v>131</v>
+        <v>17</v>
       </c>
       <c r="J51" t="inlineStr">
         <is>
@@ -2745,36 +2750,36 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Enna</t>
+          <t>Storykeeper</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>4227670180779906</t>
+          <t>1888598388471432</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>enna.care</t>
+          <t>StoryKeeper</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Mit enna bleiben Generationen verbunden: ✅ Erinnerungen schicken ✅ Große Auswahl an Unterhaltung</t>
+          <t>This Mother's Day, give her a gift that will last forever! Turn her life story into a personalized book filled with memories and love. What would she say if you asked about her most cherished moments?</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Kein Kauf, keine Einrichtung.</t>
+          <t>Sorry, we're having trouble playing this video.</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>2026-02-14</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="I52" t="n">
-        <v>128</v>
+        <v>14</v>
       </c>
       <c r="J52" t="inlineStr">
         <is>
@@ -2785,36 +2790,41 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Enna</t>
+          <t>Storykeeper</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>1545507783219388</t>
+          <t>1023631550111017</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>enna.care</t>
+          <t>StoryKeeper</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Next Level Kommunikation mit Oma 🫶 Dank enna auch ohne Smartphone: ✅ Erinnerungen schicken</t>
+          <t>Storykeeper helps capture your loved one’s voice, guiding each question and turning it into a book you’ll treasure forever. WWW.STORYKEEPER.COM Because memories fade, but stories shouldn’t.</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>✅ Große Auswahl an Unterhaltung</t>
+          <t>Because memories fade, but stories shouldn’t.</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Shop Now</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="I53" t="n">
-        <v>117</v>
+        <v>18</v>
       </c>
       <c r="J53" t="inlineStr">
         <is>
@@ -2830,7 +2840,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>1366264645392236</t>
+          <t>4293921600919808</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -2845,7 +2855,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Sorry, we're having trouble playing this video.</t>
+          <t>$99 for 1 Book &amp; 2 Copies</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
@@ -2870,7 +2880,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>1497596251413526</t>
+          <t>1305482504525889</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -2880,26 +2890,26 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Give him a lifetime of memories instead of another throwaway present. Start his StoryKeeper book today. Skip the generic Father’s Day gifts Give him a lifetime of memories.</t>
+          <t>Give more than a gift. Give your family a keepsake that grows more meaningful with time. WWW.STORYKEEPER.COM This Book Made My Dad Cry (In a Good Way).</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Give him a lifetime of memories.</t>
+          <t>This Book Made My Dad Cry (In a Good Way).</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Shop now</t>
+          <t>Shop Now</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="I55" t="n">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="J55" t="inlineStr">
         <is>
@@ -2915,7 +2925,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>26907492185598691</t>
+          <t>2373329653157461</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -2925,21 +2935,21 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Give more than a gift—give your family a keepsake that grows more meaningful with time. WWW.STORYKEEPER.UK The Gift They’ll Never Forget.</t>
+          <t>This Mother's Day, go beyond flowers! Turn her life story into a keepsake book. What if you could give her a gift that lasts forever?</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Give a gift that becomes a family heirloom—one story at a time.</t>
+          <t>$99 for 1 Book &amp; 2 Copies</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="I56" t="n">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="J56" t="inlineStr">
         <is>
@@ -2955,7 +2965,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>1888598388471432</t>
+          <t>2458868697949497</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -2970,16 +2980,16 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Sorry, we're having trouble playing this video.</t>
+          <t>$99 for 1 Book &amp; 2 Copies</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="I57" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="J57" t="inlineStr">
         <is>
@@ -2995,7 +3005,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>1023631550111017</t>
+          <t>1726022011744222</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -3005,17 +3015,17 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Storykeeper helps capture your loved one’s voice, guiding each question and turning it into a book you’ll treasure forever. WWW.STORYKEEPER.COM Because memories fade, but stories shouldn’t.</t>
+          <t>This Father’s Day, capture the stories that matter before they fade. StoryKeeper turns memories into a book your family can hold and hear. Sorry, we're having trouble playing this video.</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Because memories fade, but stories shouldn’t.</t>
+          <t>Sorry, we're having trouble playing this video.</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Shop Now</t>
+          <t>Learn more</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
@@ -3040,7 +3050,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>4293921600919808</t>
+          <t>2071219660470847</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -3050,21 +3060,26 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>This Mother's Day, give her a gift that will last forever! Turn her life story into a personalized book filled with memories and love. What would she say if you asked about her most cherished moments?</t>
+          <t>Give more than a gift. Give your family a keepsake that grows more meaningful with time. WWW.STORYKEEPER.COM This Book Made My Dad Cry (In a Good Way).</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>$99 for 1 Book &amp; 2 Copies</t>
+          <t>This Book Made My Dad Cry (In a Good Way).</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Shop Now</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="I59" t="n">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="J59" t="inlineStr">
         <is>
@@ -3080,7 +3095,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>1305482504525889</t>
+          <t>969167216028774</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -3090,17 +3105,17 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Give more than a gift. Give your family a keepsake that grows more meaningful with time. WWW.STORYKEEPER.COM This Book Made My Dad Cry (In a Good Way).</t>
+          <t>Your loved one’s stories deserve to be remembered – in their own words and in their own voice. StoryKeeper turns memories into love you can hold and hear. Sorry, we're having trouble playing this video.</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>This Book Made My Dad Cry (In a Good Way).</t>
+          <t>Sorry, we're having trouble playing this video.</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Shop Now</t>
+          <t>Learn more</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
@@ -3125,7 +3140,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>2373329653157461</t>
+          <t>1496684578006716</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -3135,21 +3150,26 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>This Mother's Day, go beyond flowers! Turn her life story into a keepsake book. What if you could give her a gift that lasts forever?</t>
+          <t>This Father’s Day, capture the stories that matter before they fade. StoryKeeper turns memories into a book your family can hold and hear. Sorry, we're having trouble playing this video.</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>$99 for 1 Book &amp; 2 Copies</t>
+          <t>Sorry, we're having trouble playing this video.</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Learn more</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="I61" t="n">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="J61" t="inlineStr">
         <is>
@@ -3165,7 +3185,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>2458868697949497</t>
+          <t>1032626569378336</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -3180,7 +3200,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>$99 for 1 Book &amp; 2 Copies</t>
+          <t>Sorry, we're having trouble playing this video.</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
@@ -3205,7 +3225,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>1726022011744222</t>
+          <t>2165050094062397</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -3250,7 +3270,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>2071219660470847</t>
+          <t>1677913043425369</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -3260,26 +3280,21 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Give more than a gift. Give your family a keepsake that grows more meaningful with time. WWW.STORYKEEPER.COM This Book Made My Dad Cry (In a Good Way).</t>
+          <t>This Mother's Day, give her a gift that will last forever! Turn her life story into a personalized book filled with memories and love. What would she say if you asked about her most cherished moments?</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>This Book Made My Dad Cry (In a Good Way).</t>
-        </is>
-      </c>
-      <c r="F64" t="inlineStr">
-        <is>
-          <t>Shop Now</t>
+          <t>$99 for 1 Book &amp; 2 Copies</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="I64" t="n">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="J64" t="inlineStr">
         <is>
@@ -3295,7 +3310,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>969167216028774</t>
+          <t>1486189692743311</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -3305,26 +3320,21 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Your loved one’s stories deserve to be remembered – in their own words and in their own voice. StoryKeeper turns memories into love you can hold and hear. Sorry, we're having trouble playing this video.</t>
+          <t>This Mother's Day, give her a gift that will last forever! Turn her life story into a personalized book filled with memories and love. What would she say if you asked about her most cherished moments?</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Sorry, we're having trouble playing this video.</t>
-        </is>
-      </c>
-      <c r="F65" t="inlineStr">
-        <is>
-          <t>Learn more</t>
+          <t>$99 for 1 Book &amp; 2 Copies</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="I65" t="n">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="J65" t="inlineStr">
         <is>
@@ -3340,7 +3350,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>1496684578006716</t>
+          <t>884035753955138</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -3350,17 +3360,17 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>This Father’s Day, capture the stories that matter before they fade. StoryKeeper turns memories into a book your family can hold and hear. Sorry, we're having trouble playing this video.</t>
+          <t>Interview by voice, add photos, and we turn it into a keepsake: two hardcovers + e-book. WWW.STORYKEEPER.COM Record. Print. Keep Forever</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Sorry, we're having trouble playing this video.</t>
+          <t>Record. Print. Keep Forever</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Learn more</t>
+          <t>Shop Now</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
@@ -3385,7 +3395,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>1032626569378336</t>
+          <t>984273724356720</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -3395,12 +3405,17 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>This Mother's Day, give her a gift that will last forever! Turn her life story into a personalized book filled with memories and love. What would she say if you asked about her most cherished moments?</t>
+          <t>Give more than a gift. Give your family a keepsake that grows more meaningful with time. WWW.STORYKEEPER.COM This Book Made My Dad Cry (In a Good Way).</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Sorry, we're having trouble playing this video.</t>
+          <t>This Book Made My Dad Cry (In a Good Way).</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Shop Now</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
@@ -3425,7 +3440,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>2165050094062397</t>
+          <t>1693195881992606</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -3435,26 +3450,21 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>This Father’s Day, capture the stories that matter before they fade. StoryKeeper turns memories into a book your family can hold and hear. Sorry, we're having trouble playing this video.</t>
+          <t>This Mother's Day, give her a gift that will last forever! Turn her life story into a personalized book filled with memories and love. What would she say if you asked about her most cherished moments?</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Sorry, we're having trouble playing this video.</t>
-        </is>
-      </c>
-      <c r="F68" t="inlineStr">
-        <is>
-          <t>Learn more</t>
+          <t>$99 for 1 Book &amp; 2 Copies</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="I68" t="n">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="J68" t="inlineStr">
         <is>
@@ -3470,7 +3480,7 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>1677913043425369</t>
+          <t>973998952205878</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -3480,21 +3490,26 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>This Mother's Day, give her a gift that will last forever! Turn her life story into a personalized book filled with memories and love. What would she say if you asked about her most cherished moments?</t>
+          <t>Your parents' stories deserve to be remembered - in their own voice, not just on a page. WWW.STORYKEEPER.COM The Only Book That Let's You Listen to Their Story.</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>$99 for 1 Book &amp; 2 Copies</t>
+          <t>The Only Book That Let's You Listen to Their Story.</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Shop Now</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="I69" t="n">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="J69" t="inlineStr">
         <is>
@@ -3510,7 +3525,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>1486189692743311</t>
+          <t>824548033811820</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -3520,21 +3535,26 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>This Mother's Day, give her a gift that will last forever! Turn her life story into a personalized book filled with memories and love. What would she say if you asked about her most cherished moments?</t>
+          <t>This Father’s Day, capture the stories that matter before they fade. StoryKeeper turns memories into a book your family can hold and hear. Sorry, we're having trouble playing this video.</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>$99 for 1 Book &amp; 2 Copies</t>
+          <t>Sorry, we're having trouble playing this video.</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Learn more</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="I70" t="n">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="J70" t="inlineStr">
         <is>
@@ -3550,7 +3570,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>884035753955138</t>
+          <t>877547294682816</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -3560,17 +3580,17 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Interview by voice, add photos, and we turn it into a keepsake: two hardcovers + e-book. WWW.STORYKEEPER.COM Record. Print. Keep Forever</t>
+          <t>Skip the typing, editing, and overwhelm. Storykeeper records voices naturally and turns them into a handcrafted book. Effortless, modern and filled with the moments that matter most. Sorry, we're having trouble playing this video.</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Record. Print. Keep Forever</t>
+          <t>Sorry, we're having trouble playing this video.</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Shop Now</t>
+          <t>Learn more</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
@@ -3595,7 +3615,7 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>984273724356720</t>
+          <t>974049545525369</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -3605,26 +3625,26 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Give more than a gift. Give your family a keepsake that grows more meaningful with time. WWW.STORYKEEPER.COM This Book Made My Dad Cry (In a Good Way).</t>
+          <t>This Father’s Day, capture the stories that matter before they fade. StoryKeeper turns memories into a book your family can hold and hear. Sorry, we're having trouble playing this video.</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>This Book Made My Dad Cry (In a Good Way).</t>
+          <t>Sorry, we're having trouble playing this video.</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Shop Now</t>
+          <t>Learn more</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="I72" t="n">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="J72" t="inlineStr">
         <is>
@@ -3640,7 +3660,7 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>1693195881992606</t>
+          <t>1307636784329203</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -3650,21 +3670,26 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>This Mother's Day, give her a gift that will last forever! Turn her life story into a personalized book filled with memories and love. What would she say if you asked about her most cherished moments?</t>
+          <t>It looks like a book, but it speaks from the heart. StoryKeeper turns voices and memories into something you can open, hold, and hear. Sorry, we're having trouble playing this video.</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>$99 for 1 Book &amp; 2 Copies</t>
+          <t>Sorry, we're having trouble playing this video.</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Learn more</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="I73" t="n">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="J73" t="inlineStr">
         <is>
@@ -3680,7 +3705,7 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>973998952205878</t>
+          <t>1314583030805433</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -3690,12 +3715,12 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Your parents' stories deserve to be remembered - in their own voice, not just on a page. WWW.STORYKEEPER.COM The Only Book That Let's You Listen to Their Story.</t>
+          <t>Interview by voice, add photos, and we turn it into a keepsake: two hardcovers + e-book. WWW.STORYKEEPER.COM Record. Print. Keep Forever</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>The Only Book That Let's You Listen to Their Story.</t>
+          <t>Record. Print. Keep Forever</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3725,7 +3750,7 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>824548033811820</t>
+          <t>1501274841477337</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -3735,26 +3760,21 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>This Father’s Day, capture the stories that matter before they fade. StoryKeeper turns memories into a book your family can hold and hear. Sorry, we're having trouble playing this video.</t>
+          <t>Ditch the flowers this Mother's Day! Create a custom book that tells her life story What if you could give her a gift she'll treasure forever?</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Sorry, we're having trouble playing this video.</t>
-        </is>
-      </c>
-      <c r="F75" t="inlineStr">
-        <is>
-          <t>Learn more</t>
+          <t>Turn memories into a lasting keepsake</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="I75" t="n">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="J75" t="inlineStr">
         <is>
@@ -3765,41 +3785,41 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Storykeeper</t>
+          <t>Heritage Whisper</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>877547294682816</t>
+          <t>1483261886675355</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>StoryKeeper</t>
+          <t>Heritage Whisper</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Skip the typing, editing, and overwhelm. Storykeeper records voices naturally and turns them into a handcrafted book. Effortless, modern and filled with the moments that matter most. Sorry, we're having trouble playing this video.</t>
+          <t>Voice-first memory sharing Voice-first memory sharing Storytelling that is captivating families worldwide</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Sorry, we're having trouble playing this video.</t>
+          <t>Storytelling that is captivating families worldwide</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Learn more</t>
+          <t>Learn More</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-04-19</t>
         </is>
       </c>
       <c r="I76" t="n">
-        <v>18</v>
+        <v>64</v>
       </c>
       <c r="J76" t="inlineStr">
         <is>
@@ -3810,22 +3830,22 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Storykeeper</t>
+          <t>ElliQ</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>974049545525369</t>
+          <t>1685628942752739</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>StoryKeeper</t>
+          <t>ElliQ</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>This Father’s Day, capture the stories that matter before they fade. StoryKeeper turns memories into a book your family can hold and hear. Sorry, we're having trouble playing this video.</t>
+          <t>Conversation, interaction, and mental stimulation are essential for cognitive health 💡 ElliQ helps support healthy aging by providing meaningful daily engagement and companionship. Sorry, we're having trouble playing this video.</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -3840,11 +3860,11 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="I77" t="n">
-        <v>18</v>
+        <v>81</v>
       </c>
       <c r="J77" t="inlineStr">
         <is>
@@ -3855,22 +3875,22 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Storykeeper</t>
+          <t>ElliQ</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>1307636784329203</t>
+          <t>1688004719222897</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>StoryKeeper</t>
+          <t>ElliQ</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>It looks like a book, but it speaks from the heart. StoryKeeper turns voices and memories into something you can open, hold, and hear. Sorry, we're having trouble playing this video.</t>
+          <t>Conversation, interaction, and mental stimulation are essential for cognitive health 💡 ElliQ helps support healthy aging by providing meaningful daily engagement and companionship. Sorry, we're having trouble playing this video.</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
@@ -3885,11 +3905,11 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="I78" t="n">
-        <v>18</v>
+        <v>73</v>
       </c>
       <c r="J78" t="inlineStr">
         <is>
@@ -3900,41 +3920,41 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Storykeeper</t>
+          <t>ElliQ</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>1314583030805433</t>
+          <t>2082672142583809</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>StoryKeeper</t>
+          <t>ElliQ</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Interview by voice, add photos, and we turn it into a keepsake: two hardcovers + e-book. WWW.STORYKEEPER.COM Record. Print. Keep Forever</t>
+          <t>There’s a lot to keep track of. ElliQ helps by sending reminders about appointments, plans, and important moments - and provides company along the way. She makes your life feel simpler and more enjoyable. Sorry, we're having trouble playing this video.</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Record. Print. Keep Forever</t>
+          <t>Sorry, we're having trouble playing this video.</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Shop Now</t>
+          <t>Learn more</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="I79" t="n">
-        <v>17</v>
+        <v>112</v>
       </c>
       <c r="J79" t="inlineStr">
         <is>
@@ -3945,36 +3965,36 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Storykeeper</t>
+          <t>ElliQ</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>1501274841477337</t>
+          <t>25522883924055159</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>StoryKeeper</t>
+          <t>ElliQ</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Ditch the flowers this Mother's Day! Create a custom book that tells her life story What if you could give her a gift she'll treasure forever?</t>
+          <t>With ElliQ, getting started takes minutes - not hours. From the moment you plug it in, ElliQ fills your home with meaningful conversation and a sense of connection that fits right into your day. ✨ Plug in and go</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Turn memories into a lasting keepsake</t>
+          <t>✨ Daily check-ins &amp; reminders</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-04-04</t>
         </is>
       </c>
       <c r="I80" t="n">
-        <v>6</v>
+        <v>79</v>
       </c>
       <c r="J80" t="inlineStr">
         <is>
@@ -3985,41 +4005,36 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Heritage Whisper</t>
+          <t>ElliQ</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>1483261886675355</t>
+          <t>838679825886616</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Heritage Whisper</t>
+          <t>ElliQ</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Voice-first memory sharing Voice-first memory sharing Storytelling that is captivating families worldwide</t>
+          <t>Because no one should feel alone. ElliQ is more than technology - she’s a companion who’s there every day to talk, laugh, and brighten your little moments. From sharing stories to telling jokes, ElliQ brings connection, comfort, and smiles right into your home.</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Storytelling that is captivating families worldwide</t>
-        </is>
-      </c>
-      <c r="F81" t="inlineStr">
-        <is>
-          <t>Learn More</t>
+          <t>✨ A friendly voice</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>2026-04-19</t>
+          <t>2026-02-21</t>
         </is>
       </c>
       <c r="I81" t="n">
-        <v>64</v>
+        <v>121</v>
       </c>
       <c r="J81" t="inlineStr">
         <is>
@@ -4035,7 +4050,7 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>1685628942752739</t>
+          <t>1693801351853966</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -4045,7 +4060,7 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Conversation, interaction, and mental stimulation are essential for cognitive health 💡 ElliQ helps support healthy aging by providing meaningful daily engagement and companionship. Sorry, we're having trouble playing this video.</t>
+          <t>Meet ElliQ, the Smart Care Device designed to support connection, engagement, and independence at home. She's more than technology. She's a companion who's there for you every day. If you're eligible, you can join the ElliQ program at no cost through your insurance plan or your local Area Agency on Aging. Check your eligibility today at www.elliq.com/DSHS</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
@@ -4053,18 +4068,13 @@
           <t>Sorry, we're having trouble playing this video.</t>
         </is>
       </c>
-      <c r="F82" t="inlineStr">
-        <is>
-          <t>Learn more</t>
-        </is>
-      </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="I82" t="n">
-        <v>81</v>
+        <v>10</v>
       </c>
       <c r="J82" t="inlineStr">
         <is>
@@ -4080,7 +4090,7 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>1688004719222897</t>
+          <t>1488992326012147</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -4090,7 +4100,7 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Conversation, interaction, and mental stimulation are essential for cognitive health 💡 ElliQ helps support healthy aging by providing meaningful daily engagement and companionship. Sorry, we're having trouble playing this video.</t>
+          <t>A friendly voice. A daily routine. A healthier mind. 💡 ElliQ helps keep minds active and spirits lifted with daily interaction, gentle prompts, and engaging moments that support long-term cognitive health. Sorry, we're having trouble playing this video.</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
@@ -4105,11 +4115,11 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="I83" t="n">
-        <v>73</v>
+        <v>42</v>
       </c>
       <c r="J83" t="inlineStr">
         <is>
@@ -4125,7 +4135,7 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>2082672142583809</t>
+          <t>1682907829804633</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -4135,7 +4145,7 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>There’s a lot to keep track of. ElliQ helps by sending reminders about appointments, plans, and important moments - and provides company along the way. She makes your life feel simpler and more enjoyable. Sorry, we're having trouble playing this video.</t>
+          <t>Conversation, interaction, and mental stimulation are essential for cognitive health 💡 ElliQ helps support healthy aging by providing meaningful daily engagement and companionship. Sorry, we're having trouble playing this video.</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
@@ -4150,11 +4160,11 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="I84" t="n">
-        <v>112</v>
+        <v>48</v>
       </c>
       <c r="J84" t="inlineStr">
         <is>
@@ -4170,7 +4180,7 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>25522883924055159</t>
+          <t>993138953210800</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -4180,21 +4190,26 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>With ElliQ, getting started takes minutes - not hours. From the moment you plug it in, ElliQ fills your home with meaningful conversation and a sense of connection that fits right into your day. ✨ Plug in and go</t>
+          <t>A friendly voice. A daily routine. A healthier mind. 💡 ElliQ helps keep minds active and spirits lifted with daily interaction, gentle prompts, and engaging moments that support long-term cognitive health. Sorry, we're having trouble playing this video.</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>✨ Daily check-ins &amp; reminders</t>
+          <t>Sorry, we're having trouble playing this video.</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>Learn more</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>2026-04-04</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="I85" t="n">
-        <v>79</v>
+        <v>47</v>
       </c>
       <c r="J85" t="inlineStr">
         <is>
@@ -4210,7 +4225,7 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>838679825886616</t>
+          <t>2383639082136267</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -4230,11 +4245,11 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>2026-02-21</t>
+          <t>2026-05-16</t>
         </is>
       </c>
       <c r="I86" t="n">
-        <v>121</v>
+        <v>37</v>
       </c>
       <c r="J86" t="inlineStr">
         <is>
@@ -4250,7 +4265,7 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>944975184903429</t>
+          <t>3778152075652558</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -4260,26 +4275,21 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>A friendly voice. A daily routine. A healthier mind. 💡 ElliQ helps keep minds active and spirits lifted with daily interaction, gentle prompts, and engaging moments that support long-term cognitive health. Sorry, we're having trouble playing this video.</t>
+          <t>Because no one should feel alone. ElliQ is more than technology - she’s a companion who’s there every day to talk, laugh, and brighten your little moments. From sharing stories to telling jokes, ElliQ brings connection, comfort, and smiles right into your home.</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Sorry, we're having trouble playing this video.</t>
-        </is>
-      </c>
-      <c r="F87" t="inlineStr">
-        <is>
-          <t>Learn more</t>
+          <t>✨ A friendly voice</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="I87" t="n">
-        <v>68</v>
+        <v>31</v>
       </c>
       <c r="J87" t="inlineStr">
         <is>
@@ -4295,7 +4305,7 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>1693801351853966</t>
+          <t>2009611493250793</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -4305,7 +4315,7 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Meet ElliQ, the Smart Care Device designed to support connection, engagement, and independence at home. She's more than technology. She's a companion who's there for you every day. If you're eligible, you can join the ElliQ program at no cost through your insurance plan or your local Area Agency on Aging. Check your eligibility today at www.elliq.com/DSHS</t>
+          <t>Meet ElliQ, the friendly robot designed to support connection, engagement, and independence at home. She's more than technology. She's a companion who's there for you every day. If you're eligible, you can join the ElliQ program at no cost through your local Area Agency on Aging. Check your eligibility today at www.elliq.com/free</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
@@ -4315,468 +4325,13 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="I88" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="J88" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="inlineStr">
-        <is>
-          <t>ElliQ</t>
-        </is>
-      </c>
-      <c r="B89" t="inlineStr">
-        <is>
-          <t>1488992326012147</t>
-        </is>
-      </c>
-      <c r="C89" t="inlineStr">
-        <is>
-          <t>ElliQ</t>
-        </is>
-      </c>
-      <c r="D89" t="inlineStr">
-        <is>
-          <t>A friendly voice. A daily routine. A healthier mind. 💡 ElliQ helps keep minds active and spirits lifted with daily interaction, gentle prompts, and engaging moments that support long-term cognitive health. Sorry, we're having trouble playing this video.</t>
-        </is>
-      </c>
-      <c r="E89" t="inlineStr">
-        <is>
-          <t>Sorry, we're having trouble playing this video.</t>
-        </is>
-      </c>
-      <c r="F89" t="inlineStr">
-        <is>
-          <t>Learn more</t>
-        </is>
-      </c>
-      <c r="G89" t="inlineStr">
-        <is>
-          <t>2026-05-11</t>
-        </is>
-      </c>
-      <c r="I89" t="n">
-        <v>42</v>
-      </c>
-      <c r="J89" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="inlineStr">
-        <is>
-          <t>ElliQ</t>
-        </is>
-      </c>
-      <c r="B90" t="inlineStr">
-        <is>
-          <t>1948413482455351</t>
-        </is>
-      </c>
-      <c r="C90" t="inlineStr">
-        <is>
-          <t>ElliQ</t>
-        </is>
-      </c>
-      <c r="D90" t="inlineStr">
-        <is>
-          <t>What if the way we think about aging actually impacts how we age? The research suggests it does. Positive aging isn’t just a mindset. It can shape real outcomes. That's why ElliQ focuses on helping people feel capable, connected, active, and engaged every day. The goal isn’t just helping people age at home.</t>
-        </is>
-      </c>
-      <c r="E90" t="inlineStr">
-        <is>
-          <t>It’s helping them continue to thrive there ✨</t>
-        </is>
-      </c>
-      <c r="G90" t="inlineStr">
-        <is>
-          <t>2026-05-15</t>
-        </is>
-      </c>
-      <c r="I90" t="n">
-        <v>38</v>
-      </c>
-      <c r="J90" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" t="inlineStr">
-        <is>
-          <t>ElliQ</t>
-        </is>
-      </c>
-      <c r="B91" t="inlineStr">
-        <is>
-          <t>1682907829804633</t>
-        </is>
-      </c>
-      <c r="C91" t="inlineStr">
-        <is>
-          <t>ElliQ</t>
-        </is>
-      </c>
-      <c r="D91" t="inlineStr">
-        <is>
-          <t>Conversation, interaction, and mental stimulation are essential for cognitive health 💡 ElliQ helps support healthy aging by providing meaningful daily engagement and companionship. Sorry, we're having trouble playing this video.</t>
-        </is>
-      </c>
-      <c r="E91" t="inlineStr">
-        <is>
-          <t>Sorry, we're having trouble playing this video.</t>
-        </is>
-      </c>
-      <c r="F91" t="inlineStr">
-        <is>
-          <t>Learn more</t>
-        </is>
-      </c>
-      <c r="G91" t="inlineStr">
-        <is>
-          <t>2026-05-05</t>
-        </is>
-      </c>
-      <c r="I91" t="n">
-        <v>48</v>
-      </c>
-      <c r="J91" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" t="inlineStr">
-        <is>
-          <t>ElliQ</t>
-        </is>
-      </c>
-      <c r="B92" t="inlineStr">
-        <is>
-          <t>993138953210800</t>
-        </is>
-      </c>
-      <c r="C92" t="inlineStr">
-        <is>
-          <t>ElliQ</t>
-        </is>
-      </c>
-      <c r="D92" t="inlineStr">
-        <is>
-          <t>A friendly voice. A daily routine. A healthier mind. 💡 ElliQ helps keep minds active and spirits lifted with daily interaction, gentle prompts, and engaging moments that support long-term cognitive health. Sorry, we're having trouble playing this video.</t>
-        </is>
-      </c>
-      <c r="E92" t="inlineStr">
-        <is>
-          <t>Sorry, we're having trouble playing this video.</t>
-        </is>
-      </c>
-      <c r="F92" t="inlineStr">
-        <is>
-          <t>Learn more</t>
-        </is>
-      </c>
-      <c r="G92" t="inlineStr">
-        <is>
-          <t>2026-05-06</t>
-        </is>
-      </c>
-      <c r="I92" t="n">
-        <v>47</v>
-      </c>
-      <c r="J92" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="inlineStr">
-        <is>
-          <t>ElliQ</t>
-        </is>
-      </c>
-      <c r="B93" t="inlineStr">
-        <is>
-          <t>1502915464761878</t>
-        </is>
-      </c>
-      <c r="C93" t="inlineStr">
-        <is>
-          <t>ElliQ</t>
-        </is>
-      </c>
-      <c r="D93" t="inlineStr">
-        <is>
-          <t>Because no one should feel alone. ElliQ is more than technology - she’s a companion who’s there every day to talk, laugh, and brighten your little moments. From sharing stories to telling jokes, ElliQ brings connection, comfort, and smiles right into your home.</t>
-        </is>
-      </c>
-      <c r="E93" t="inlineStr">
-        <is>
-          <t>✨ A friendly voice</t>
-        </is>
-      </c>
-      <c r="G93" t="inlineStr">
-        <is>
-          <t>2026-04-23</t>
-        </is>
-      </c>
-      <c r="I93" t="n">
-        <v>60</v>
-      </c>
-      <c r="J93" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" t="inlineStr">
-        <is>
-          <t>ElliQ</t>
-        </is>
-      </c>
-      <c r="B94" t="inlineStr">
-        <is>
-          <t>26794090103575688</t>
-        </is>
-      </c>
-      <c r="C94" t="inlineStr">
-        <is>
-          <t>ElliQ</t>
-        </is>
-      </c>
-      <c r="D94" t="inlineStr">
-        <is>
-          <t>What if the way we think about aging actually impacts how we age? The research suggests it does. Positive aging isn’t just a mindset. It can shape real outcomes. That's why ElliQ focuses on helping people feel capable, connected, active, and engaged every day. The goal isn’t just helping people age at home.</t>
-        </is>
-      </c>
-      <c r="E94" t="inlineStr">
-        <is>
-          <t>It’s helping them continue to thrive there ✨</t>
-        </is>
-      </c>
-      <c r="G94" t="inlineStr">
-        <is>
-          <t>2026-05-19</t>
-        </is>
-      </c>
-      <c r="I94" t="n">
-        <v>34</v>
-      </c>
-      <c r="J94" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="inlineStr">
-        <is>
-          <t>ElliQ</t>
-        </is>
-      </c>
-      <c r="B95" t="inlineStr">
-        <is>
-          <t>2383639082136267</t>
-        </is>
-      </c>
-      <c r="C95" t="inlineStr">
-        <is>
-          <t>ElliQ</t>
-        </is>
-      </c>
-      <c r="D95" t="inlineStr">
-        <is>
-          <t>Because no one should feel alone. ElliQ is more than technology - she’s a companion who’s there every day to talk, laugh, and brighten your little moments. From sharing stories to telling jokes, ElliQ brings connection, comfort, and smiles right into your home.</t>
-        </is>
-      </c>
-      <c r="E95" t="inlineStr">
-        <is>
-          <t>✨ A friendly voice</t>
-        </is>
-      </c>
-      <c r="G95" t="inlineStr">
-        <is>
-          <t>2026-05-16</t>
-        </is>
-      </c>
-      <c r="I95" t="n">
-        <v>37</v>
-      </c>
-      <c r="J95" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" t="inlineStr">
-        <is>
-          <t>ElliQ</t>
-        </is>
-      </c>
-      <c r="B96" t="inlineStr">
-        <is>
-          <t>1544424053867984</t>
-        </is>
-      </c>
-      <c r="C96" t="inlineStr">
-        <is>
-          <t>ElliQ</t>
-        </is>
-      </c>
-      <c r="D96" t="inlineStr">
-        <is>
-          <t>Because no one should feel alone. ElliQ is more than technology - she’s a companion who’s there every day to talk, laugh, and brighten your little moments. From sharing stories to telling jokes, ElliQ brings connection, comfort, and smiles right into your home.</t>
-        </is>
-      </c>
-      <c r="E96" t="inlineStr">
-        <is>
-          <t>✨ A friendly voice</t>
-        </is>
-      </c>
-      <c r="G96" t="inlineStr">
-        <is>
-          <t>2026-06-15</t>
-        </is>
-      </c>
-      <c r="I96" t="n">
-        <v>7</v>
-      </c>
-      <c r="J96" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" t="inlineStr">
-        <is>
-          <t>ElliQ</t>
-        </is>
-      </c>
-      <c r="B97" t="inlineStr">
-        <is>
-          <t>1369220495124467</t>
-        </is>
-      </c>
-      <c r="C97" t="inlineStr">
-        <is>
-          <t>ElliQ</t>
-        </is>
-      </c>
-      <c r="D97" t="inlineStr">
-        <is>
-          <t>More independence. More connection. More life. ElliQ helps bring structure, conversation, and joy into everyday routines - without feeling complicated. ✨ Friendly daily check-ins</t>
-        </is>
-      </c>
-      <c r="E97" t="inlineStr">
-        <is>
-          <t>✨ Gentle reminders &amp; encouragement</t>
-        </is>
-      </c>
-      <c r="G97" t="inlineStr">
-        <is>
-          <t>2026-05-18</t>
-        </is>
-      </c>
-      <c r="I97" t="n">
-        <v>35</v>
-      </c>
-      <c r="J97" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" t="inlineStr">
-        <is>
-          <t>ElliQ</t>
-        </is>
-      </c>
-      <c r="B98" t="inlineStr">
-        <is>
-          <t>1426272895929547</t>
-        </is>
-      </c>
-      <c r="C98" t="inlineStr">
-        <is>
-          <t>ElliQ</t>
-        </is>
-      </c>
-      <c r="D98" t="inlineStr">
-        <is>
-          <t>Because no one should feel alone. ElliQ is more than technology - she’s a companion who’s there every day to talk, laugh, and brighten your little moments. From sharing stories to telling jokes, ElliQ brings connection, comfort, and smiles right into your home.</t>
-        </is>
-      </c>
-      <c r="E98" t="inlineStr">
-        <is>
-          <t>✨ A friendly voice</t>
-        </is>
-      </c>
-      <c r="G98" t="inlineStr">
-        <is>
-          <t>2026-06-15</t>
-        </is>
-      </c>
-      <c r="I98" t="n">
-        <v>7</v>
-      </c>
-      <c r="J98" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" t="inlineStr">
-        <is>
-          <t>ElliQ</t>
-        </is>
-      </c>
-      <c r="B99" t="inlineStr">
-        <is>
-          <t>3778152075652558</t>
-        </is>
-      </c>
-      <c r="C99" t="inlineStr">
-        <is>
-          <t>ElliQ</t>
-        </is>
-      </c>
-      <c r="D99" t="inlineStr">
-        <is>
-          <t>Because no one should feel alone. ElliQ is more than technology - she’s a companion who’s there every day to talk, laugh, and brighten your little moments. From sharing stories to telling jokes, ElliQ brings connection, comfort, and smiles right into your home.</t>
-        </is>
-      </c>
-      <c r="E99" t="inlineStr">
-        <is>
-          <t>✨ A friendly voice</t>
-        </is>
-      </c>
-      <c r="G99" t="inlineStr">
-        <is>
-          <t>2026-05-22</t>
-        </is>
-      </c>
-      <c r="I99" t="n">
-        <v>31</v>
-      </c>
-      <c r="J99" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -4793,7 +4348,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B45"/>
+  <dimension ref="A1:B40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="41" customWidth="1" min="1" max="1"/>
@@ -4810,7 +4365,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Generated: 2026-06-22 11:07 UTC</t>
+          <t>Generated: 2026-06-22 17:48 UTC</t>
         </is>
       </c>
     </row>
@@ -4829,7 +4384,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>37</v>
+        <v>32</v>
       </c>
     </row>
     <row r="6">
@@ -4839,7 +4394,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>42</v>
+        <v>48</v>
       </c>
     </row>
     <row r="7"/>
@@ -4902,208 +4457,173 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>1369220495124467</t>
+          <t>1483261886675355</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>1426272895929547</t>
+          <t>1486189692743311</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>1483261886675355</t>
+          <t>1497596251413526</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>1486189692743311</t>
+          <t>1501274841477337</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>1497596251413526</t>
+          <t>1545507783219388</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>1501274841477337</t>
+          <t>1555465969317444</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>1502915464761878</t>
+          <t>1677913043425369</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>1544424053867984</t>
+          <t>1693195881992606</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>1545507783219388</t>
+          <t>1693801351853966</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>1555465969317444</t>
+          <t>1786057292771309</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>1677913043425369</t>
+          <t>1913150252681632</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>1693195881992606</t>
+          <t>1932125440830258</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>1693801351853966</t>
+          <t>2009611493250793</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>1786057292771309</t>
+          <t>2129791074419999</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>1913150252681632</t>
+          <t>2132037480708829</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>1932125440830258</t>
+          <t>2222090038553123</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2129791074419999</t>
+          <t>2248159552601062</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2132037480708829</t>
+          <t>2337622166699478</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2222090038553123</t>
+          <t>2373329653157461</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2248159552601062</t>
+          <t>2458868697949497</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2337622166699478</t>
+          <t>4227670180779906</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2373329653157461</t>
+          <t>4293921600919808</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2458868697949497</t>
+          <t>877547294682816</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2589188208165366</t>
+          <t>879770831200211</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
-        <is>
-          <t>2915078732162013</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>4227670180779906</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>4293921600919808</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>877547294682816</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>879770831200211</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
         <is>
           <t>984273724356720</t>
         </is>
